--- a/동안거.xlsx
+++ b/동안거.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\bgpogyo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE85721-488E-4F7C-B059-C9E10A0EE098}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A99C99-6A84-48B7-92A8-29ACB8DAEA83}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="개요" sheetId="1" r:id="rId1"/>
     <sheet name="목차" sheetId="2" r:id="rId2"/>
     <sheet name="사경" sheetId="3" r:id="rId3"/>
   </sheets>
